--- a/config/xlsx/expedition.xlsx
+++ b/config/xlsx/expedition.xlsx
@@ -500,16 +500,12 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="E2" s="3" t="inlineStr"/>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -531,16 +527,12 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -562,16 +554,12 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>70</v>
+        <v>700</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="E4" s="3" t="inlineStr"/>
       <c r="F4" s="3" t="inlineStr">
         <is>
           <t>21;22</t>
@@ -598,11 +586,7 @@
       <c r="D5" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -629,11 +613,7 @@
       <c r="D6" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="E6" s="3" t="inlineStr"/>
       <c r="F6" s="3" t="inlineStr">
         <is>
           <t>22;61</t>
@@ -660,11 +640,7 @@
       <c r="D7" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -691,11 +667,7 @@
       <c r="D8" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="E8" s="3" t="inlineStr"/>
       <c r="F8" s="3" t="inlineStr">
         <is>
           <t>22;71</t>
@@ -722,11 +694,7 @@
       <c r="D9" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
           <t>21;71</t>
@@ -753,11 +721,7 @@
       <c r="D10" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="E10" s="3" t="inlineStr"/>
       <c r="F10" s="3" t="inlineStr">
         <is>
           <t>81;71;22</t>
@@ -784,11 +748,7 @@
       <c r="D11" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr">
         <is>
           <t>81;81;71</t>
@@ -815,11 +775,7 @@
       <c r="D12" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="E12" s="3" t="inlineStr"/>
       <c r="F12" s="3" t="inlineStr">
         <is>
           <t>81;81;81;71</t>
